--- a/business_forms/036_monthly_business_plan_form_template--business_forms.xlsx
+++ b/business_forms/036_monthly_business_plan_form_template--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'january'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'January'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'february'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'February'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'march'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'March'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'april'}</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'April'}</t>
+          <t>April</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'may'}</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'May'}</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'june'}</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'June'}</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'july'}</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'July'}</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'august'}</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'August'}</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'september'}</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'September'}</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'october'}</t>
+          <t>october</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'October'}</t>
+          <t>October</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'november'}</t>
+          <t>november</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'November'}</t>
+          <t>November</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'december'}</t>
+          <t>december</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'December'}</t>
+          <t>December</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'goal_1'}</t>
+          <t>goal_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Goal 1'}</t>
+          <t>Goal 1</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'goal_2'}</t>
+          <t>goal_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Goal 2'}</t>
+          <t>Goal 2</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'goal_3'}</t>
+          <t>goal_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Goal 3'}</t>
+          <t>Goal 3</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'goal_4'}</t>
+          <t>goal_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Goal 4'}</t>
+          <t>Goal 4</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'goal_5'}</t>
+          <t>goal_5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Goal 5'}</t>
+          <t>Goal 5</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'business_forms'}</t>
+          <t>business_forms</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Business Forms'}</t>
+          <t>Business Forms</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tracking_forms'}</t>
+          <t>tracking_forms</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tracking Forms'}</t>
+          <t>Tracking Forms</t>
         </is>
       </c>
     </row>
